--- a/data/raw/sales/Week 33/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 33/Audio_Array/other_channels.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B2B" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flipkart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blinkit Sales" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D2C - Audio Array" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flipkart" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,24 +466,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FBA79815</t>
+          <t>FBA75675</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>AM-C3</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>1759.38</v>
+        <v>1700</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -492,26 +494,110 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>FBA79005</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B0CKHVHVQ1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AM-W45</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3" t="n">
+        <v>194995</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FBA79815</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>B0FPR7VFCH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AM-W19</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1759.38</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>FBA79816</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>B0FPR962YS</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>AM-W22</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>28858.43</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FBA79825</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B0FJ2DT13L</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GB-02 (AM-C43 + AI-11)</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="n">
-        <v>11516.8</v>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E6" t="n">
+        <v>5529.95</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Audio Array</t>
         </is>
@@ -528,6 +614,434 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ASIN</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sale Amount</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FBA75673</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B0B4DPX2J2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AM-C1</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>13495</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FBA76864</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B0BPLZ5CGV</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AI-04 Red</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9398</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FBA79005</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>B0CKHVHVQ1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AM-W45</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4999</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FBA79107</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B0CM9P5CCK</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AM-W17</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11245</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FBA79108</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B0CM9L1QZG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AM-W16</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1399</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FBA79109</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B0CM9HYVDM</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AM-W18</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2598</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FBA79380</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>B0D3M1B4Z8</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AM-C46</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11097</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FBA79958</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B0G3Q59X8C</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AM-W24</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1999</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ASIN</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sale Amount</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FBA75673</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B0B4DPX2J2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AM-C1</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5049.8</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FBA79482</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B0DXFPM4N2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AM-S1</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4499</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FBA79839</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>B0FQBXS6Y2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AH-45 BK</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2760.2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FBA79958</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B0G3Q59X8C</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AM-W24</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1761.7</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/data/raw/sales/Week 33/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 33/Audio_Array/other_channels.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
         <v>50</v>
       </c>
       <c r="E3" t="n">
-        <v>194995</v>
+        <v>165250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -522,24 +522,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FBA79815</t>
+          <t>FBA79109</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>AM-W18</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1759.38</v>
+        <v>2551.58</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -550,24 +550,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FBA79816</t>
+          <t>FBA79815</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>28858.43</v>
+        <v>1491</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -578,26 +578,138 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>FBA79816</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B0FPR962YS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AM-W22</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" t="n">
+        <v>45773.03</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>FBA79825</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>B0FJ2DT13L</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>GB-02 (AM-C43 + AI-11)</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>5529.95</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FBA79909</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>B0FVM17Q4W</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AM-W20</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11864.4</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FBA79972</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B0GCP1J2HC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>50423.7</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FBA80085</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B0GXPBHDRF</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>21355.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Audio Array</t>
         </is>
